--- a/Notebooks/banking_analysis_results.xlsx
+++ b/Notebooks/banking_analysis_results.xlsx
@@ -7,26 +7,30 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="q1_districts" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="q2_gender" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="q3_district_age" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="q4_yearly_trends" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="q5_transaction_types" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="q6_monthly_activity" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="q7_monthly_trends" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="q8_account_types" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="q9_recent_transactions" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="q10_high_balances" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="q11_loan_status" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="q12_loan_amounts" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="q13_loans_by_account" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="q14_card_types" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="q15_low_activity" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="q16_high_transactions" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="q17_district_salary" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="q18_data_quality" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="q19_avg_amount" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="q20_no_transactions" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="query_01" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="02_top 5 districts by customer" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="03_average salary per district" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="query_04" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="query_05" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="query_06" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="07_monthly transaction trends" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="08_transaction summary by type" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="09_transaction summary by opera" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="query_10" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="query_11" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="query_12" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="query_13" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="query_14" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="query_15" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="query_16" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="query_17" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="query_18" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="query_19" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="query_20" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="query_21" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="query_22" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="query_23" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="query_24" sheetId="24" state="visible" r:id="rId24"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1234,244 +1238,115 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>account_id</t>
+          <t>transaction_month</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>balance</t>
+          <t>transaction_count</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>10520</v>
-      </c>
-      <c r="B2" s="2" t="n">
-        <v>43957</v>
-      </c>
-      <c r="C2" t="n">
-        <v>209637</v>
+        <v>1</v>
+      </c>
+      <c r="B2" t="n">
+        <v>122214</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>9052</v>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>43897</v>
-      </c>
-      <c r="C3" t="n">
-        <v>196106.5</v>
+        <v>12</v>
+      </c>
+      <c r="B3" t="n">
+        <v>94775</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1029</v>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>44317</v>
-      </c>
-      <c r="C4" t="n">
-        <v>194119.3</v>
+        <v>11</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91890</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2176</v>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>42584</v>
-      </c>
-      <c r="C5" t="n">
-        <v>193909.9</v>
+        <v>10</v>
+      </c>
+      <c r="B5" t="n">
+        <v>90839</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>10520</v>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>43960</v>
-      </c>
-      <c r="C6" t="n">
-        <v>189765</v>
+        <v>6</v>
+      </c>
+      <c r="B6" t="n">
+        <v>88276</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>10079</v>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>42883</v>
-      </c>
-      <c r="C7" t="n">
-        <v>189714.3</v>
+        <v>9</v>
+      </c>
+      <c r="B7" t="n">
+        <v>87955</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>4276</v>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>43691</v>
-      </c>
-      <c r="C8" t="n">
-        <v>188635.1</v>
+        <v>8</v>
+      </c>
+      <c r="B8" t="n">
+        <v>86204</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>863</v>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>43598</v>
-      </c>
-      <c r="C9" t="n">
-        <v>188348.2</v>
+        <v>7</v>
+      </c>
+      <c r="B9" t="n">
+        <v>83791</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1828</v>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>43426</v>
-      </c>
-      <c r="C10" t="n">
-        <v>186881.3</v>
+        <v>5</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79931</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>10520</v>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>43957</v>
-      </c>
-      <c r="C11" t="n">
-        <v>185780</v>
+        <v>3</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79922</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>3364</v>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>44421</v>
-      </c>
-      <c r="C12" t="n">
-        <v>184988.5</v>
+        <v>4</v>
+      </c>
+      <c r="B12" t="n">
+        <v>76954</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2099</v>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>42661</v>
-      </c>
-      <c r="C13" t="n">
-        <v>184168.4</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>1139</v>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>44159</v>
-      </c>
-      <c r="C14" t="n">
-        <v>183702</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>9627</v>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>44373</v>
-      </c>
-      <c r="C15" t="n">
-        <v>180290</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>390</v>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>44150</v>
-      </c>
-      <c r="C16" t="n">
-        <v>179943.4</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>1485</v>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>44536</v>
-      </c>
-      <c r="C17" t="n">
-        <v>178774.4</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>239</v>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>43772</v>
-      </c>
-      <c r="C18" t="n">
-        <v>178670.2</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>4276</v>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>44473</v>
-      </c>
-      <c r="C19" t="n">
-        <v>177532.6</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>500</v>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>43729</v>
-      </c>
-      <c r="C20" t="n">
-        <v>177018.4</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>319</v>
-      </c>
-      <c r="B21" s="2" t="n">
-        <v>44260</v>
-      </c>
-      <c r="C21" t="n">
-        <v>176868.7</v>
+        <v>2</v>
+      </c>
+      <c r="B13" t="n">
+        <v>65824</v>
       </c>
     </row>
   </sheetData>
@@ -1485,59 +1360,816 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:C73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>transaction_year</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>total_loans</t>
+          <t>transaction_month</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>transaction_count</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
+      <c r="A2" t="n">
+        <v>2016</v>
       </c>
       <c r="B2" t="n">
-        <v>403</v>
+        <v>1</v>
+      </c>
+      <c r="C2" t="n">
+        <v>177</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
+      <c r="A3" t="n">
+        <v>2016</v>
       </c>
       <c r="B3" t="n">
-        <v>203</v>
+        <v>2</v>
+      </c>
+      <c r="C3" t="n">
+        <v>395</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
+      <c r="A4" t="n">
+        <v>2016</v>
       </c>
       <c r="B4" t="n">
-        <v>45</v>
+        <v>3</v>
+      </c>
+      <c r="C4" t="n">
+        <v>676</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
+      <c r="A5" t="n">
+        <v>2016</v>
       </c>
       <c r="B5" t="n">
-        <v>31</v>
+        <v>4</v>
+      </c>
+      <c r="C5" t="n">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1306</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1880</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C8" t="n">
+        <v>2399</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B9" t="n">
+        <v>8</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2938</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B10" t="n">
+        <v>9</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3441</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B11" t="n">
+        <v>10</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3989</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B12" t="n">
+        <v>11</v>
+      </c>
+      <c r="C12" t="n">
+        <v>4422</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B13" t="n">
+        <v>12</v>
+      </c>
+      <c r="C13" t="n">
+        <v>5669</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="n">
+        <v>9139</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B15" t="n">
+        <v>2</v>
+      </c>
+      <c r="C15" t="n">
+        <v>5601</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B16" t="n">
+        <v>3</v>
+      </c>
+      <c r="C16" t="n">
+        <v>6255</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B17" t="n">
+        <v>4</v>
+      </c>
+      <c r="C17" t="n">
+        <v>6549</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B18" t="n">
+        <v>5</v>
+      </c>
+      <c r="C18" t="n">
+        <v>7059</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B19" t="n">
+        <v>6</v>
+      </c>
+      <c r="C19" t="n">
+        <v>7916</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B20" t="n">
+        <v>7</v>
+      </c>
+      <c r="C20" t="n">
+        <v>7398</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B21" t="n">
+        <v>8</v>
+      </c>
+      <c r="C21" t="n">
+        <v>7600</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B22" t="n">
+        <v>9</v>
+      </c>
+      <c r="C22" t="n">
+        <v>7844</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B23" t="n">
+        <v>10</v>
+      </c>
+      <c r="C23" t="n">
+        <v>8197</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B24" t="n">
+        <v>11</v>
+      </c>
+      <c r="C24" t="n">
+        <v>8275</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B25" t="n">
+        <v>12</v>
+      </c>
+      <c r="C25" t="n">
+        <v>9795</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" t="n">
+        <v>15493</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B27" t="n">
+        <v>2</v>
+      </c>
+      <c r="C27" t="n">
+        <v>8682</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B28" t="n">
+        <v>3</v>
+      </c>
+      <c r="C28" t="n">
+        <v>9304</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B29" t="n">
+        <v>4</v>
+      </c>
+      <c r="C29" t="n">
+        <v>9519</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B30" t="n">
+        <v>5</v>
+      </c>
+      <c r="C30" t="n">
+        <v>9938</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B31" t="n">
+        <v>6</v>
+      </c>
+      <c r="C31" t="n">
+        <v>10930</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B32" t="n">
+        <v>7</v>
+      </c>
+      <c r="C32" t="n">
+        <v>10431</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B33" t="n">
+        <v>8</v>
+      </c>
+      <c r="C33" t="n">
+        <v>10766</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B34" t="n">
+        <v>9</v>
+      </c>
+      <c r="C34" t="n">
+        <v>11013</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B35" t="n">
+        <v>10</v>
+      </c>
+      <c r="C35" t="n">
+        <v>11431</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B36" t="n">
+        <v>11</v>
+      </c>
+      <c r="C36" t="n">
+        <v>11741</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B37" t="n">
+        <v>12</v>
+      </c>
+      <c r="C37" t="n">
+        <v>13774</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B38" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" t="n">
+        <v>21405</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B39" t="n">
+        <v>2</v>
+      </c>
+      <c r="C39" t="n">
+        <v>7949</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B40" t="n">
+        <v>3</v>
+      </c>
+      <c r="C40" t="n">
+        <v>17855</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B41" t="n">
+        <v>4</v>
+      </c>
+      <c r="C41" t="n">
+        <v>13754</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B42" t="n">
+        <v>5</v>
+      </c>
+      <c r="C42" t="n">
+        <v>14308</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B43" t="n">
+        <v>6</v>
+      </c>
+      <c r="C43" t="n">
+        <v>15885</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B44" t="n">
+        <v>7</v>
+      </c>
+      <c r="C44" t="n">
+        <v>15500</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B45" t="n">
+        <v>8</v>
+      </c>
+      <c r="C45" t="n">
+        <v>16299</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B46" t="n">
+        <v>9</v>
+      </c>
+      <c r="C46" t="n">
+        <v>16883</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B47" t="n">
+        <v>10</v>
+      </c>
+      <c r="C47" t="n">
+        <v>17538</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B48" t="n">
+        <v>11</v>
+      </c>
+      <c r="C48" t="n">
+        <v>17943</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B49" t="n">
+        <v>12</v>
+      </c>
+      <c r="C49" t="n">
+        <v>21460</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B50" t="n">
+        <v>1</v>
+      </c>
+      <c r="C50" t="n">
+        <v>33060</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B51" t="n">
+        <v>2</v>
+      </c>
+      <c r="C51" t="n">
+        <v>19202</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B52" t="n">
+        <v>3</v>
+      </c>
+      <c r="C52" t="n">
+        <v>20491</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B53" t="n">
+        <v>4</v>
+      </c>
+      <c r="C53" t="n">
+        <v>20922</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B54" t="n">
+        <v>5</v>
+      </c>
+      <c r="C54" t="n">
+        <v>21686</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B55" t="n">
+        <v>6</v>
+      </c>
+      <c r="C55" t="n">
+        <v>23832</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B56" t="n">
+        <v>7</v>
+      </c>
+      <c r="C56" t="n">
+        <v>22481</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B57" t="n">
+        <v>8</v>
+      </c>
+      <c r="C57" t="n">
+        <v>22979</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B58" t="n">
+        <v>9</v>
+      </c>
+      <c r="C58" t="n">
+        <v>23324</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B59" t="n">
+        <v>10</v>
+      </c>
+      <c r="C59" t="n">
+        <v>23995</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B60" t="n">
+        <v>11</v>
+      </c>
+      <c r="C60" t="n">
+        <v>24168</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B61" t="n">
+        <v>12</v>
+      </c>
+      <c r="C61" t="n">
+        <v>28269</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B62" t="n">
+        <v>1</v>
+      </c>
+      <c r="C62" t="n">
+        <v>42940</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B63" t="n">
+        <v>2</v>
+      </c>
+      <c r="C63" t="n">
+        <v>23995</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B64" t="n">
+        <v>3</v>
+      </c>
+      <c r="C64" t="n">
+        <v>25341</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B65" t="n">
+        <v>4</v>
+      </c>
+      <c r="C65" t="n">
+        <v>25297</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B66" t="n">
+        <v>5</v>
+      </c>
+      <c r="C66" t="n">
+        <v>25634</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B67" t="n">
+        <v>6</v>
+      </c>
+      <c r="C67" t="n">
+        <v>27833</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B68" t="n">
+        <v>7</v>
+      </c>
+      <c r="C68" t="n">
+        <v>25582</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B69" t="n">
+        <v>8</v>
+      </c>
+      <c r="C69" t="n">
+        <v>25622</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B70" t="n">
+        <v>9</v>
+      </c>
+      <c r="C70" t="n">
+        <v>25450</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B71" t="n">
+        <v>10</v>
+      </c>
+      <c r="C71" t="n">
+        <v>25689</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B72" t="n">
+        <v>11</v>
+      </c>
+      <c r="C72" t="n">
+        <v>25341</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B73" t="n">
+        <v>12</v>
+      </c>
+      <c r="C73" t="n">
+        <v>15808</v>
       </c>
     </row>
   </sheetData>
@@ -1551,93 +2183,159 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>account_type</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>total_loans</t>
+          <t>frequency</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>total_loan_amount</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>average_loan_amount</t>
+          <t>total_accounts</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>403</v>
+          <t>Savings account</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>POPLATEK MESICNE</t>
+        </is>
       </c>
       <c r="C2" t="n">
-        <v>69078372</v>
-      </c>
-      <c r="D2" t="n">
-        <v>171410.35</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>203</v>
+          <t>NRI account</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>POPLATEK MESICNE</t>
+        </is>
       </c>
       <c r="C3" t="n">
-        <v>18603216</v>
-      </c>
-      <c r="D3" t="n">
-        <v>91641.46000000001</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>45</v>
+          <t>Salary account</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>POPLATEK MESICNE</t>
+        </is>
       </c>
       <c r="C4" t="n">
-        <v>11217804</v>
-      </c>
-      <c r="D4" t="n">
-        <v>249284.53</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>31</v>
+          <t>NRI account</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>POPLATEK TYDNE</t>
+        </is>
       </c>
       <c r="C5" t="n">
-        <v>4362348</v>
-      </c>
-      <c r="D5" t="n">
-        <v>140720.9</v>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Salary account</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>POPLATEK TYDNE</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Savings account</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>POPLATEK TYDNE</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>NRI account</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>POPLATEK PO OBRATU</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Salary account</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>POPLATEK PO OBRATU</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Savings account</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>POPLATEK PO OBRATU</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -1651,63 +2349,284 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>account_type</t>
+          <t>account_id</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>total_loans</t>
+          <t>date</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>total_loan_amount</t>
+          <t>balance</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Salary account</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>229</v>
-      </c>
-      <c r="C2" t="n">
-        <v>35017140</v>
+      <c r="A2" t="n">
+        <v>5891</v>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>44549</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>114092.00</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>NRI account</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>217</v>
-      </c>
-      <c r="C3" t="n">
-        <v>34527708</v>
+      <c r="A3" t="n">
+        <v>96</v>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>44549</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>91988.30</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Savings account</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>236</v>
-      </c>
-      <c r="C4" t="n">
-        <v>33716892</v>
+      <c r="A4" t="n">
+        <v>3787</v>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>44549</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>81497.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>7614</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>44549</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>62788.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>108</v>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>44549</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>60420.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3791</v>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>44549</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>60146.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3779</v>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>44549</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>59783.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>122</v>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>44549</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>57562.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>2367</v>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>44549</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>57462.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>170</v>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>44549</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>57083.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>3064</v>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>44549</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>55907.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3048</v>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>44549</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>49768.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1886</v>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>44549</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>49077.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>160</v>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>44549</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>48645.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>3789</v>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>44549</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>44784.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>1889</v>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>44549</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>41407.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>11362</v>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>44549</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>38367.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>7753</v>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>44549</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>34252.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>3789</v>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>44549</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>33684.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>3056</v>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>44549</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>32856.30</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1721,49 +2640,284 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>card_type</t>
+          <t>account_id</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>total_cards</t>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>balance</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>classic</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>659</v>
+      <c r="A2" t="n">
+        <v>10520</v>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>43957</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>209637.00</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>junior</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>145</v>
+      <c r="A3" t="n">
+        <v>9052</v>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>43897</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>196106.50</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>gold</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>88</v>
+      <c r="A4" t="n">
+        <v>1029</v>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>44317</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>194119.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2176</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>42584</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>193909.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>10520</v>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>43960</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>189765.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>10079</v>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>42883</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>189714.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>4276</v>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>43691</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>188635.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>863</v>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>43598</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>188348.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1828</v>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>43426</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>186881.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10520</v>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>43957</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>185780.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>3364</v>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>44421</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>184988.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>2099</v>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>42661</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>184168.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1139</v>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>44159</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>183702.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>9627</v>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>44373</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>180290.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>390</v>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>44150</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>179943.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>1485</v>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>44536</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>178774.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>239</v>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>43772</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>178670.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>4276</v>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>44473</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>177532.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>500</v>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>43729</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>177018.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>319</v>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>44260</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>176868.70</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1777,179 +2931,59 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>account_id</t>
+          <t>status</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>total_transactions</t>
+          <t>total_loans</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>182</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="B2" t="n">
-        <v>9</v>
+        <v>403</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>727</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
       </c>
       <c r="B3" t="n">
-        <v>11</v>
+        <v>203</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>315</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
       </c>
       <c r="B4" t="n">
-        <v>11</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>758</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="B5" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>1430</v>
-      </c>
-      <c r="B6" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>1563</v>
-      </c>
-      <c r="B7" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>3715</v>
-      </c>
-      <c r="B8" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>2892</v>
-      </c>
-      <c r="B9" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>3616</v>
-      </c>
-      <c r="B10" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>2300</v>
-      </c>
-      <c r="B11" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>869</v>
-      </c>
-      <c r="B12" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>1720</v>
-      </c>
-      <c r="B13" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>2021</v>
-      </c>
-      <c r="B14" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>1454</v>
-      </c>
-      <c r="B15" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>672</v>
-      </c>
-      <c r="B16" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>3461</v>
-      </c>
-      <c r="B17" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>476</v>
-      </c>
-      <c r="B18" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>585</v>
-      </c>
-      <c r="B19" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>1735</v>
-      </c>
-      <c r="B20" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>3716</v>
-      </c>
-      <c r="B21" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -1963,414 +2997,109 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>trans_id</t>
+          <t>status</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>account_id</t>
+          <t>total_loans</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>total_loan_amount</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>amount</t>
+          <t>average_loan_amount</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>291346</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="B2" t="n">
-        <v>998</v>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>44545</v>
+        <v>403</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>69078372</t>
+        </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Withdrawal</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>87400</v>
+          <t>171410.3524</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>1306770</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
       </c>
       <c r="B3" t="n">
-        <v>4462</v>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>44353</v>
+        <v>203</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>18603216</t>
+        </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Withdrawal</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>87300</v>
+          <t>91641.4581</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>855512</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
       </c>
       <c r="B4" t="n">
-        <v>2915</v>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>43630</v>
+        <v>45</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>11217804</t>
+        </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Withdrawal</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>86400</v>
+          <t>249284.5333</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>1207200</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="B5" t="n">
-        <v>4130</v>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>44366</v>
+        <v>31</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>4362348</t>
+        </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Withdrawal</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>85800</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>1170721</v>
-      </c>
-      <c r="B6" t="n">
-        <v>4014</v>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>44362</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Withdrawal</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>81900</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>1137293</v>
-      </c>
-      <c r="B7" t="n">
-        <v>3886</v>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>43996</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Withdrawal</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>80700</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>1248236</v>
-      </c>
-      <c r="B8" t="n">
-        <v>4269</v>
-      </c>
-      <c r="C8" s="2" t="n">
-        <v>43644</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Withdrawal</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>80700</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>115552</v>
-      </c>
-      <c r="B9" t="n">
-        <v>390</v>
-      </c>
-      <c r="C9" s="2" t="n">
-        <v>44004</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Withdrawal</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>80400</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>2648606</v>
-      </c>
-      <c r="B10" t="n">
-        <v>8759</v>
-      </c>
-      <c r="C10" s="2" t="n">
-        <v>43258</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Withdrawal</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>80400</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>706371</v>
-      </c>
-      <c r="B11" t="n">
-        <v>2419</v>
-      </c>
-      <c r="C11" s="2" t="n">
-        <v>44357</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Withdrawal</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>80100</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>761187</v>
-      </c>
-      <c r="B12" t="n">
-        <v>2598</v>
-      </c>
-      <c r="C12" s="2" t="n">
-        <v>43636</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Withdrawal</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>78900</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>960855</v>
-      </c>
-      <c r="B13" t="n">
-        <v>3273</v>
-      </c>
-      <c r="C13" s="2" t="n">
-        <v>43637</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Withdrawal</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>78900</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>1309216</v>
-      </c>
-      <c r="B14" t="n">
-        <v>4470</v>
-      </c>
-      <c r="C14" s="2" t="n">
-        <v>43271</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Withdrawal</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>78900</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>1075778</v>
-      </c>
-      <c r="B15" t="n">
-        <v>3675</v>
-      </c>
-      <c r="C15" s="2" t="n">
-        <v>44007</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Withdrawal</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>78600</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>3354528</v>
-      </c>
-      <c r="B16" t="n">
-        <v>11141</v>
-      </c>
-      <c r="C16" s="2" t="n">
-        <v>43990</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Withdrawal</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>78600</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>141211</v>
-      </c>
-      <c r="B17" t="n">
-        <v>472</v>
-      </c>
-      <c r="C17" s="2" t="n">
-        <v>44372</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Withdrawal</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>78300</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>2586466</v>
-      </c>
-      <c r="B18" t="n">
-        <v>8547</v>
-      </c>
-      <c r="C18" s="2" t="n">
-        <v>43639</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Withdrawal</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>78300</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>1155373</v>
-      </c>
-      <c r="B19" t="n">
-        <v>3953</v>
-      </c>
-      <c r="C19" s="2" t="n">
-        <v>44365</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Withdrawal</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>78000</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>3183668</v>
-      </c>
-      <c r="B20" t="n">
-        <v>10562</v>
-      </c>
-      <c r="C20" s="2" t="n">
-        <v>43985</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Withdrawal</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>78000</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>1669417</v>
-      </c>
-      <c r="B21" t="n">
-        <v>5661</v>
-      </c>
-      <c r="C21" s="2" t="n">
-        <v>43630</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Withdrawal</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>77700</v>
+          <t>140720.9032</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -2384,1012 +3113,69 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C77"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>district_name</t>
+          <t>account_type</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>average_salary</t>
+          <t>total_loans</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>total_customers</t>
+          <t>total_loan_amount</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Hl.m. Praha</t>
+          <t>Salary account</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12541</v>
-      </c>
-      <c r="C2" t="n">
-        <v>663</v>
+        <v>229</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>35017140</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Mlada Boleslav</t>
+          <t>NRI account</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11277</v>
-      </c>
-      <c r="C3" t="n">
-        <v>69</v>
+        <v>217</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>34527708</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Plzen - mesto</t>
+          <t>Savings account</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10787</v>
-      </c>
-      <c r="C4" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Ostrava - mesto</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>10673</v>
-      </c>
-      <c r="C5" t="n">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Most</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>10446</v>
-      </c>
-      <c r="C6" t="n">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Karvina</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>10177</v>
-      </c>
-      <c r="C7" t="n">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Praha - vychod</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>10124</v>
-      </c>
-      <c r="C8" t="n">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Ceske Budejovice</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>10045</v>
-      </c>
-      <c r="C9" t="n">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Melnik</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>9920</v>
-      </c>
-      <c r="C10" t="n">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Brno - mesto</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>9897</v>
-      </c>
-      <c r="C11" t="n">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Frydek - Mistek</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>9893</v>
-      </c>
-      <c r="C12" t="n">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Usti nad Labem</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>9832</v>
-      </c>
-      <c r="C13" t="n">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Kladno</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>9753</v>
-      </c>
-      <c r="C14" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Chomutov</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>9675</v>
-      </c>
-      <c r="C15" t="n">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Sokolov</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>9650</v>
-      </c>
-      <c r="C16" t="n">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Zlin</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>9624</v>
-      </c>
-      <c r="C17" t="n">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Praha - zapad</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>9622</v>
-      </c>
-      <c r="C18" t="n">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Pardubice</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>9538</v>
-      </c>
-      <c r="C19" t="n">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Hradec Kralove</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>9425</v>
-      </c>
-      <c r="C20" t="n">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Teplice</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>9317</v>
-      </c>
-      <c r="C21" t="n">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Kolin</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>9307</v>
-      </c>
-      <c r="C22" t="n">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Ceska Lipa</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>9272</v>
-      </c>
-      <c r="C23" t="n">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Liberec</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>9198</v>
-      </c>
-      <c r="C24" t="n">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Tabor</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>9104</v>
-      </c>
-      <c r="C25" t="n">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Litomerice</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>9065</v>
-      </c>
-      <c r="C26" t="n">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Rychnov nad Kneznou</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>9060</v>
-      </c>
-      <c r="C27" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Cesky Krumlov</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>9045</v>
-      </c>
-      <c r="C28" t="n">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Olomouc</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>8994</v>
-      </c>
-      <c r="C29" t="n">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Karlovy Vary</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>8991</v>
-      </c>
-      <c r="C30" t="n">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Beroun</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>8980</v>
-      </c>
-      <c r="C31" t="n">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Pisek</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>8968</v>
-      </c>
-      <c r="C32" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Louny</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>8965</v>
-      </c>
-      <c r="C33" t="n">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Tachov</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>8930</v>
-      </c>
-      <c r="C34" t="n">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Vsetin</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>8909</v>
-      </c>
-      <c r="C35" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Nymburk</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>8899</v>
-      </c>
-      <c r="C36" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Jablonec n. Nisou</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>8867</v>
-      </c>
-      <c r="C37" t="n">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Rokycany</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>8843</v>
-      </c>
-      <c r="C38" t="n">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Prerov</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>8819</v>
-      </c>
-      <c r="C39" t="n">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Trebic</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>8814</v>
-      </c>
-      <c r="C40" t="n">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Breclav</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>8772</v>
-      </c>
-      <c r="C41" t="n">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Jihlava</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>8757</v>
-      </c>
-      <c r="C42" t="n">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Pribram</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
-        <v>8754</v>
-      </c>
-      <c r="C43" t="n">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Opava</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
-        <v>8746</v>
-      </c>
-      <c r="C44" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Brno - venkov</t>
-        </is>
-      </c>
-      <c r="B45" t="n">
-        <v>8743</v>
-      </c>
-      <c r="C45" t="n">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Hodonin</t>
-        </is>
-      </c>
-      <c r="B46" t="n">
-        <v>8720</v>
-      </c>
-      <c r="C46" t="n">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Decin</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
-        <v>8705</v>
-      </c>
-      <c r="C47" t="n">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Novy Jicin</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
-        <v>8678</v>
-      </c>
-      <c r="C48" t="n">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Cheb</t>
-        </is>
-      </c>
-      <c r="B49" t="n">
-        <v>8624</v>
-      </c>
-      <c r="C49" t="n">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Domazlice</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
-        <v>8620</v>
-      </c>
-      <c r="C50" t="n">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Rakovnik</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>8598</v>
-      </c>
-      <c r="C51" t="n">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Plzen - sever</t>
-        </is>
-      </c>
-      <c r="B52" t="n">
-        <v>8594</v>
-      </c>
-      <c r="C52" t="n">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Plzen - jih</t>
-        </is>
-      </c>
-      <c r="B53" t="n">
-        <v>8561</v>
-      </c>
-      <c r="C53" t="n">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Klatovy</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
-        <v>8554</v>
-      </c>
-      <c r="C54" t="n">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Strakonice</t>
-        </is>
-      </c>
-      <c r="B55" t="n">
-        <v>8547</v>
-      </c>
-      <c r="C55" t="n">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Kutna Hora</t>
-        </is>
-      </c>
-      <c r="B56" t="n">
-        <v>8546</v>
-      </c>
-      <c r="C56" t="n">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Uherske Hradiste</t>
-        </is>
-      </c>
-      <c r="B57" t="n">
-        <v>8544</v>
-      </c>
-      <c r="C57" t="n">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Trutnov</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>8541</v>
-      </c>
-      <c r="C58" t="n">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Zdar nad Sazavou</t>
-        </is>
-      </c>
-      <c r="B59" t="n">
-        <v>8512</v>
-      </c>
-      <c r="C59" t="n">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Benesov</t>
-        </is>
-      </c>
-      <c r="B60" t="n">
-        <v>8507</v>
-      </c>
-      <c r="C60" t="n">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Kromeriz</t>
-        </is>
-      </c>
-      <c r="B61" t="n">
-        <v>8444</v>
-      </c>
-      <c r="C61" t="n">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Prostejov</t>
-        </is>
-      </c>
-      <c r="B62" t="n">
-        <v>8441</v>
-      </c>
-      <c r="C62" t="n">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Jindrichuv Hradec</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>8427</v>
-      </c>
-      <c r="C63" t="n">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Znojmo</t>
-        </is>
-      </c>
-      <c r="B64" t="n">
-        <v>8403</v>
-      </c>
-      <c r="C64" t="n">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Prachatice</t>
-        </is>
-      </c>
-      <c r="B65" t="n">
-        <v>8402</v>
-      </c>
-      <c r="C65" t="n">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Jicin</t>
-        </is>
-      </c>
-      <c r="B66" t="n">
-        <v>8390</v>
-      </c>
-      <c r="C66" t="n">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Havlickuv Brod</t>
-        </is>
-      </c>
-      <c r="B67" t="n">
-        <v>8388</v>
-      </c>
-      <c r="C67" t="n">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Sumperk</t>
-        </is>
-      </c>
-      <c r="B68" t="n">
-        <v>8369</v>
-      </c>
-      <c r="C68" t="n">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Nachod</t>
-        </is>
-      </c>
-      <c r="B69" t="n">
-        <v>8369</v>
-      </c>
-      <c r="C69" t="n">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Usti nad Orlici</t>
-        </is>
-      </c>
-      <c r="B70" t="n">
-        <v>8363</v>
-      </c>
-      <c r="C70" t="n">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Vyskov</t>
-        </is>
-      </c>
-      <c r="B71" t="n">
-        <v>8288</v>
-      </c>
-      <c r="C71" t="n">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Chrudim</t>
-        </is>
-      </c>
-      <c r="B72" t="n">
-        <v>8254</v>
-      </c>
-      <c r="C72" t="n">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Blansko</t>
-        </is>
-      </c>
-      <c r="B73" t="n">
-        <v>8240</v>
-      </c>
-      <c r="C73" t="n">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Semily</t>
-        </is>
-      </c>
-      <c r="B74" t="n">
-        <v>8208</v>
-      </c>
-      <c r="C74" t="n">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Svitavy</t>
-        </is>
-      </c>
-      <c r="B75" t="n">
-        <v>8187</v>
-      </c>
-      <c r="C75" t="n">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Pelhrimov</t>
-        </is>
-      </c>
-      <c r="B76" t="n">
-        <v>8114</v>
-      </c>
-      <c r="C76" t="n">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Bruntal</t>
-        </is>
-      </c>
-      <c r="B77" t="n">
-        <v>8110</v>
-      </c>
-      <c r="C77" t="n">
-        <v>45</v>
+        <v>236</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>33716892</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -3403,51 +3189,49 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>total_rows</t>
+          <t>card_type</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>missing_transaction_ids</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>missing_account_ids</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>missing_dates</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>missing_amounts</t>
+          <t>total_cards</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>1048575</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>classic</t>
+        </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0</v>
+        <v>659</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>junior</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>gold</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -3461,50 +3245,179 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>transaction_type</t>
+          <t>account_id</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>transaction_count</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>average_amount</t>
+          <t>total_transactions</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Credit</t>
-        </is>
+      <c r="A2" t="n">
+        <v>182</v>
       </c>
       <c r="B2" t="n">
-        <v>400209</v>
-      </c>
-      <c r="C2" t="n">
-        <v>8036.64</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Withdrawal</t>
-        </is>
+      <c r="A3" t="n">
+        <v>727</v>
       </c>
       <c r="B3" t="n">
-        <v>648366</v>
-      </c>
-      <c r="C3" t="n">
-        <v>4649.31</v>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>315</v>
+      </c>
+      <c r="B4" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>758</v>
+      </c>
+      <c r="B5" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1430</v>
+      </c>
+      <c r="B6" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1563</v>
+      </c>
+      <c r="B7" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3715</v>
+      </c>
+      <c r="B8" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2892</v>
+      </c>
+      <c r="B9" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>3616</v>
+      </c>
+      <c r="B10" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>2300</v>
+      </c>
+      <c r="B11" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>869</v>
+      </c>
+      <c r="B12" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1720</v>
+      </c>
+      <c r="B13" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B14" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>1454</v>
+      </c>
+      <c r="B15" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>672</v>
+      </c>
+      <c r="B16" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>3461</v>
+      </c>
+      <c r="B17" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>476</v>
+      </c>
+      <c r="B18" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>585</v>
+      </c>
+      <c r="B19" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>1735</v>
+      </c>
+      <c r="B20" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>3716</v>
+      </c>
+      <c r="B21" t="n">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -3518,13 +3431,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>gender</t>
+          <t>district_name</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -3541,27 +3454,76 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>Hl.m. Praha</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2645</v>
-      </c>
-      <c r="C2" t="n">
-        <v>49.26</v>
+        <v>663</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>12.35</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>Ostrava - mesto</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2724</v>
-      </c>
-      <c r="C3" t="n">
-        <v>50.74</v>
+        <v>180</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>3.35</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Karvina</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>169</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>3.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Brno - mesto</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>155</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2.89</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Zlin</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>109</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -3575,6 +3537,1613 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>trans_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>account_id</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>291346</v>
+      </c>
+      <c r="B2" t="n">
+        <v>998</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>44545</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Withdrawal</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>87400.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1306770</v>
+      </c>
+      <c r="B3" t="n">
+        <v>4462</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>44353</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Withdrawal</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>87300.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>855512</v>
+      </c>
+      <c r="B4" t="n">
+        <v>2915</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>43630</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Withdrawal</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>86400.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1207200</v>
+      </c>
+      <c r="B5" t="n">
+        <v>4130</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>44366</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Withdrawal</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>85800.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1170721</v>
+      </c>
+      <c r="B6" t="n">
+        <v>4014</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>44362</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Withdrawal</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>81900.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1137293</v>
+      </c>
+      <c r="B7" t="n">
+        <v>3886</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>43996</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Withdrawal</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>80700.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1248236</v>
+      </c>
+      <c r="B8" t="n">
+        <v>4269</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>43644</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Withdrawal</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>80700.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>115552</v>
+      </c>
+      <c r="B9" t="n">
+        <v>390</v>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>44004</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Withdrawal</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>80400.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>2648606</v>
+      </c>
+      <c r="B10" t="n">
+        <v>8759</v>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>43258</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Withdrawal</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>80400.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>706371</v>
+      </c>
+      <c r="B11" t="n">
+        <v>2419</v>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>44357</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Withdrawal</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>80100.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>761187</v>
+      </c>
+      <c r="B12" t="n">
+        <v>2598</v>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>43636</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Withdrawal</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>78900.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>960855</v>
+      </c>
+      <c r="B13" t="n">
+        <v>3273</v>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>43637</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Withdrawal</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>78900.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1309216</v>
+      </c>
+      <c r="B14" t="n">
+        <v>4470</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>43271</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Withdrawal</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>78900.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>1075778</v>
+      </c>
+      <c r="B15" t="n">
+        <v>3675</v>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>44007</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Withdrawal</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>78600.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>3354528</v>
+      </c>
+      <c r="B16" t="n">
+        <v>11141</v>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>43990</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Withdrawal</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>78600.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>141211</v>
+      </c>
+      <c r="B17" t="n">
+        <v>472</v>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>44372</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Withdrawal</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>78300.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>2586466</v>
+      </c>
+      <c r="B18" t="n">
+        <v>8547</v>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>43639</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Withdrawal</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>78300.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>1155373</v>
+      </c>
+      <c r="B19" t="n">
+        <v>3953</v>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>44365</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Withdrawal</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>78000.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>3183668</v>
+      </c>
+      <c r="B20" t="n">
+        <v>10562</v>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>43985</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Withdrawal</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>78000.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>1669417</v>
+      </c>
+      <c r="B21" t="n">
+        <v>5661</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>43630</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Withdrawal</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>77700.00</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C77"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>district_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>average_salary</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>total_customers</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Hl.m. Praha</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>12541</v>
+      </c>
+      <c r="C2" t="n">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Mlada Boleslav</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>11277</v>
+      </c>
+      <c r="C3" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Plzen - mesto</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>10787</v>
+      </c>
+      <c r="C4" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Ostrava - mesto</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>10673</v>
+      </c>
+      <c r="C5" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Most</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>10446</v>
+      </c>
+      <c r="C6" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Karvina</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>10177</v>
+      </c>
+      <c r="C7" t="n">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Praha - vychod</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>10124</v>
+      </c>
+      <c r="C8" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Ceske Budejovice</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>10045</v>
+      </c>
+      <c r="C9" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Melnik</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>9920</v>
+      </c>
+      <c r="C10" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Brno - mesto</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>9897</v>
+      </c>
+      <c r="C11" t="n">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Frydek - Mistek</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>9893</v>
+      </c>
+      <c r="C12" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Usti nad Labem</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>9832</v>
+      </c>
+      <c r="C13" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Kladno</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>9753</v>
+      </c>
+      <c r="C14" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Chomutov</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>9675</v>
+      </c>
+      <c r="C15" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Sokolov</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>9650</v>
+      </c>
+      <c r="C16" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Zlin</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>9624</v>
+      </c>
+      <c r="C17" t="n">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Praha - zapad</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>9622</v>
+      </c>
+      <c r="C18" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Pardubice</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>9538</v>
+      </c>
+      <c r="C19" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Hradec Kralove</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>9425</v>
+      </c>
+      <c r="C20" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Teplice</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>9317</v>
+      </c>
+      <c r="C21" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Kolin</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>9307</v>
+      </c>
+      <c r="C22" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Ceska Lipa</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>9272</v>
+      </c>
+      <c r="C23" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Liberec</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>9198</v>
+      </c>
+      <c r="C24" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Tabor</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>9104</v>
+      </c>
+      <c r="C25" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Litomerice</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>9065</v>
+      </c>
+      <c r="C26" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Rychnov nad Kneznou</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>9060</v>
+      </c>
+      <c r="C27" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Cesky Krumlov</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>9045</v>
+      </c>
+      <c r="C28" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Olomouc</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>8994</v>
+      </c>
+      <c r="C29" t="n">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Karlovy Vary</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>8991</v>
+      </c>
+      <c r="C30" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Beroun</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>8980</v>
+      </c>
+      <c r="C31" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Pisek</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>8968</v>
+      </c>
+      <c r="C32" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Louny</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>8965</v>
+      </c>
+      <c r="C33" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Tachov</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>8930</v>
+      </c>
+      <c r="C34" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Vsetin</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>8909</v>
+      </c>
+      <c r="C35" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Nymburk</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>8899</v>
+      </c>
+      <c r="C36" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Jablonec n. Nisou</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>8867</v>
+      </c>
+      <c r="C37" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Rokycany</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>8843</v>
+      </c>
+      <c r="C38" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Prerov</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>8819</v>
+      </c>
+      <c r="C39" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trebic</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>8814</v>
+      </c>
+      <c r="C40" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Breclav</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>8772</v>
+      </c>
+      <c r="C41" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Jihlava</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>8757</v>
+      </c>
+      <c r="C42" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Pribram</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>8754</v>
+      </c>
+      <c r="C43" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Opava</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>8746</v>
+      </c>
+      <c r="C44" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Brno - venkov</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>8743</v>
+      </c>
+      <c r="C45" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Hodonin</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>8720</v>
+      </c>
+      <c r="C46" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Decin</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>8705</v>
+      </c>
+      <c r="C47" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Novy Jicin</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>8678</v>
+      </c>
+      <c r="C48" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Cheb</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>8624</v>
+      </c>
+      <c r="C49" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Domazlice</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>8620</v>
+      </c>
+      <c r="C50" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Rakovnik</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>8598</v>
+      </c>
+      <c r="C51" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Plzen - sever</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>8594</v>
+      </c>
+      <c r="C52" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Plzen - jih</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>8561</v>
+      </c>
+      <c r="C53" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Klatovy</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>8554</v>
+      </c>
+      <c r="C54" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Strakonice</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>8547</v>
+      </c>
+      <c r="C55" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Kutna Hora</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>8546</v>
+      </c>
+      <c r="C56" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Uherske Hradiste</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>8544</v>
+      </c>
+      <c r="C57" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Trutnov</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>8541</v>
+      </c>
+      <c r="C58" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Zdar nad Sazavou</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>8512</v>
+      </c>
+      <c r="C59" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Benesov</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>8507</v>
+      </c>
+      <c r="C60" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Kromeriz</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>8444</v>
+      </c>
+      <c r="C61" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Prostejov</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>8441</v>
+      </c>
+      <c r="C62" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Jindrichuv Hradec</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>8427</v>
+      </c>
+      <c r="C63" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Znojmo</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>8403</v>
+      </c>
+      <c r="C64" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Prachatice</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>8402</v>
+      </c>
+      <c r="C65" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Jicin</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>8390</v>
+      </c>
+      <c r="C66" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Havlickuv Brod</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>8388</v>
+      </c>
+      <c r="C67" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Sumperk</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>8369</v>
+      </c>
+      <c r="C68" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Nachod</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>8369</v>
+      </c>
+      <c r="C69" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Usti nad Orlici</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>8363</v>
+      </c>
+      <c r="C70" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Vyskov</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>8288</v>
+      </c>
+      <c r="C71" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Chrudim</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>8254</v>
+      </c>
+      <c r="C72" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>8240</v>
+      </c>
+      <c r="C73" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Semily</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>8208</v>
+      </c>
+      <c r="C74" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Svitavy</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>8187</v>
+      </c>
+      <c r="C75" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Pelhrimov</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>8114</v>
+      </c>
+      <c r="C76" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Bruntal</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>8110</v>
+      </c>
+      <c r="C77" t="n">
+        <v>45</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>total_rows</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>missing_transaction_ids</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>missing_account_ids</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>missing_dates</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>missing_amounts</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1048575</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>transaction_type</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>transaction_count</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>average_amount</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Credit</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>400209</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>8036.64</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Withdrawal</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>648366</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>4649.31</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -3601,7 +5170,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B77"/>
+  <dimension ref="A1:C77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3612,768 +5181,1001 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>average_age</t>
+          <t>average_salary</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>total_customers</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Chomutov</t>
+          <t>Hl.m. Praha</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>76.7</v>
+        <v>12541</v>
+      </c>
+      <c r="C2" t="n">
+        <v>663</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Brno - venkov</t>
+          <t>Ostrava - mesto</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>75.09999999999999</v>
+        <v>10673</v>
+      </c>
+      <c r="C3" t="n">
+        <v>180</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Bruntal</t>
+          <t>Karvina</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>73.59999999999999</v>
+        <v>10177</v>
+      </c>
+      <c r="C4" t="n">
+        <v>169</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Praha - vychod</t>
+          <t>Brno - mesto</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>72.90000000000001</v>
+        <v>9897</v>
+      </c>
+      <c r="C5" t="n">
+        <v>155</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Olomouc</t>
+          <t>Zlin</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>72.90000000000001</v>
+        <v>9624</v>
+      </c>
+      <c r="C6" t="n">
+        <v>109</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Prerov</t>
+          <t>Olomouc</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>72.09999999999999</v>
+        <v>8994</v>
+      </c>
+      <c r="C7" t="n">
+        <v>104</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Rakovnik</t>
+          <t>Frydek - Mistek</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>72</v>
+        <v>9893</v>
+      </c>
+      <c r="C8" t="n">
+        <v>86</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Klatovy</t>
+          <t>Nachod</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>71.90000000000001</v>
+        <v>8369</v>
+      </c>
+      <c r="C9" t="n">
+        <v>76</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Decin</t>
+          <t>Usti nad Orlici</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>71.8</v>
+        <v>8363</v>
+      </c>
+      <c r="C10" t="n">
+        <v>73</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sumperk</t>
+          <t>Kolin</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>71.8</v>
+        <v>9307</v>
+      </c>
+      <c r="C11" t="n">
+        <v>71</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Mlada Boleslav</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>71.5</v>
+        <v>11277</v>
+      </c>
+      <c r="C12" t="n">
+        <v>69</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Karlovy Vary</t>
+          <t>Decin</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>71.09999999999999</v>
+        <v>8705</v>
+      </c>
+      <c r="C13" t="n">
+        <v>69</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Hodonin</t>
+          <t>Liberec</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>70.59999999999999</v>
+        <v>9198</v>
+      </c>
+      <c r="C14" t="n">
+        <v>67</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Trutnov</t>
+          <t>Prachatice</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>70.59999999999999</v>
+        <v>8402</v>
+      </c>
+      <c r="C15" t="n">
+        <v>66</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Tabor</t>
+          <t>Zdar nad Sazavou</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>70.5</v>
+        <v>8512</v>
+      </c>
+      <c r="C16" t="n">
+        <v>66</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Praha - zapad</t>
+          <t>Louny</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>70.40000000000001</v>
+        <v>8965</v>
+      </c>
+      <c r="C17" t="n">
+        <v>65</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Prachatice</t>
+          <t>Kromeriz</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>70.3</v>
+        <v>8444</v>
+      </c>
+      <c r="C18" t="n">
+        <v>64</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Frydek - Mistek</t>
+          <t>Brno - venkov</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>70.3</v>
+        <v>8743</v>
+      </c>
+      <c r="C19" t="n">
+        <v>63</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sokolov</t>
+          <t>Beroun</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>70.2</v>
+        <v>8980</v>
+      </c>
+      <c r="C20" t="n">
+        <v>63</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Semily</t>
+          <t>Cesky Krumlov</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>70.2</v>
+        <v>9045</v>
+      </c>
+      <c r="C21" t="n">
+        <v>63</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Pribram</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>70.09999999999999</v>
+        <v>9538</v>
+      </c>
+      <c r="C22" t="n">
+        <v>63</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Kutna Hora</t>
+          <t>Jindrichuv Hradec</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>70.09999999999999</v>
+        <v>8427</v>
+      </c>
+      <c r="C23" t="n">
+        <v>61</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Vyskov</t>
+          <t>Sumperk</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>69.90000000000001</v>
+        <v>8369</v>
+      </c>
+      <c r="C24" t="n">
+        <v>61</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Znojmo</t>
+          <t>Svitavy</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>69.90000000000001</v>
+        <v>8187</v>
+      </c>
+      <c r="C25" t="n">
+        <v>61</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Jihlava</t>
+          <t>Prostejov</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>69.8</v>
+        <v>8441</v>
+      </c>
+      <c r="C26" t="n">
+        <v>61</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Ceska Lipa</t>
+          <t>Trutnov</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>69.7</v>
+        <v>8541</v>
+      </c>
+      <c r="C27" t="n">
+        <v>61</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Beroun</t>
+          <t>Nymburk</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>69.7</v>
+        <v>8899</v>
+      </c>
+      <c r="C28" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Zlin</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>69.59999999999999</v>
+        <v>8746</v>
+      </c>
+      <c r="C29" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Novy Jicin</t>
+          <t>Rychnov nad Kneznou</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>69.59999999999999</v>
+        <v>9060</v>
+      </c>
+      <c r="C30" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Jindrichuv Hradec</t>
+          <t>Pisek</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>69.5</v>
+        <v>8968</v>
+      </c>
+      <c r="C31" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Tachov</t>
+          <t>Uherske Hradiste</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>69.3</v>
+        <v>8544</v>
+      </c>
+      <c r="C32" t="n">
+        <v>59</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Pelhrimov</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>69.3</v>
+        <v>9317</v>
+      </c>
+      <c r="C33" t="n">
+        <v>59</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Svitavy</t>
+          <t>Havlickuv Brod</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>69.09999999999999</v>
+        <v>8388</v>
+      </c>
+      <c r="C34" t="n">
+        <v>59</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Domazlice</t>
+          <t>Tachov</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>69</v>
+        <v>8930</v>
+      </c>
+      <c r="C35" t="n">
+        <v>59</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Hl.m. Praha</t>
+          <t>Tabor</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>68.90000000000001</v>
+        <v>9104</v>
+      </c>
+      <c r="C36" t="n">
+        <v>57</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Karvina</t>
+          <t>Blansko</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>68.90000000000001</v>
+        <v>8240</v>
+      </c>
+      <c r="C37" t="n">
+        <v>57</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Nachod</t>
+          <t>Praha - zapad</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>68.90000000000001</v>
+        <v>9622</v>
+      </c>
+      <c r="C38" t="n">
+        <v>56</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>Vyskov</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>68.8</v>
+        <v>8288</v>
+      </c>
+      <c r="C39" t="n">
+        <v>56</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Jablonec n. Nisou</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>68.8</v>
+        <v>8867</v>
+      </c>
+      <c r="C40" t="n">
+        <v>56</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Zdar nad Sazavou</t>
+          <t>Prerov</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>68.7</v>
+        <v>8819</v>
+      </c>
+      <c r="C41" t="n">
+        <v>56</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Plzen - mesto</t>
+          <t>Hradec Kralove</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>68.59999999999999</v>
+        <v>9425</v>
+      </c>
+      <c r="C42" t="n">
+        <v>55</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Jicin</t>
+          <t>Ceska Lipa</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>68.59999999999999</v>
+        <v>9272</v>
+      </c>
+      <c r="C43" t="n">
+        <v>55</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Strakonice</t>
+          <t>Plzen - jih</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>68.59999999999999</v>
+        <v>8561</v>
+      </c>
+      <c r="C44" t="n">
+        <v>55</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Hradec Kralove</t>
+          <t>Pelhrimov</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>68.5</v>
+        <v>8114</v>
+      </c>
+      <c r="C45" t="n">
+        <v>54</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Louny</t>
+          <t>Breclav</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>68.40000000000001</v>
+        <v>8772</v>
+      </c>
+      <c r="C46" t="n">
+        <v>54</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Vsetin</t>
+          <t>Trebic</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>68.3</v>
+        <v>8814</v>
+      </c>
+      <c r="C47" t="n">
+        <v>54</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Cheb</t>
+          <t>Plzen - sever</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>68.3</v>
+        <v>8594</v>
+      </c>
+      <c r="C48" t="n">
+        <v>54</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Rokycany</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>68.09999999999999</v>
+        <v>8843</v>
+      </c>
+      <c r="C49" t="n">
+        <v>54</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Ceske Budejovice</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>68.09999999999999</v>
+        <v>8254</v>
+      </c>
+      <c r="C50" t="n">
+        <v>54</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Ostrava - mesto</t>
+          <t>Praha - vychod</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>68</v>
+        <v>10124</v>
+      </c>
+      <c r="C51" t="n">
+        <v>54</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Rakovnik</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>68</v>
+        <v>8598</v>
+      </c>
+      <c r="C52" t="n">
+        <v>53</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Havlickuv Brod</t>
+          <t>Kutna Hora</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>67.90000000000001</v>
+        <v>8546</v>
+      </c>
+      <c r="C53" t="n">
+        <v>53</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Melnik</t>
+          <t>Cheb</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>67.8</v>
+        <v>8624</v>
+      </c>
+      <c r="C54" t="n">
+        <v>53</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Kromeriz</t>
+          <t>Jicin</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>67.59999999999999</v>
+        <v>8390</v>
+      </c>
+      <c r="C55" t="n">
+        <v>52</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Brno - mesto</t>
+          <t>Most</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>67.5</v>
+        <v>10446</v>
+      </c>
+      <c r="C56" t="n">
+        <v>52</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Kolin</t>
+          <t>Hodonin</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>67.40000000000001</v>
+        <v>8720</v>
+      </c>
+      <c r="C57" t="n">
+        <v>51</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Uherske Hradiste</t>
+          <t>Domazlice</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>67.40000000000001</v>
+        <v>8620</v>
+      </c>
+      <c r="C58" t="n">
+        <v>51</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Cesky Krumlov</t>
+          <t>Vsetin</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>67.3</v>
+        <v>8909</v>
+      </c>
+      <c r="C59" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Jablonec n. Nisou</t>
+          <t>Plzen - mesto</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>67.3</v>
+        <v>10787</v>
+      </c>
+      <c r="C60" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Rokycany</t>
+          <t>Kladno</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>66.8</v>
+        <v>9753</v>
+      </c>
+      <c r="C61" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Prostejov</t>
+          <t>Klatovy</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>66.7</v>
+        <v>8554</v>
+      </c>
+      <c r="C62" t="n">
+        <v>48</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Plzen - jih</t>
+          <t>Litomerice</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>66.59999999999999</v>
+        <v>9065</v>
+      </c>
+      <c r="C63" t="n">
+        <v>48</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Most</t>
+          <t>Sokolov</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>66.59999999999999</v>
+        <v>9650</v>
+      </c>
+      <c r="C64" t="n">
+        <v>48</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Usti nad Orlici</t>
+          <t>Novy Jicin</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>66.3</v>
+        <v>8678</v>
+      </c>
+      <c r="C65" t="n">
+        <v>48</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Mlada Boleslav</t>
+          <t>Semily</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>66.3</v>
+        <v>8208</v>
+      </c>
+      <c r="C66" t="n">
+        <v>46</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Plzen - sever</t>
+          <t>Benesov</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>66.3</v>
+        <v>8507</v>
+      </c>
+      <c r="C67" t="n">
+        <v>46</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Litomerice</t>
+          <t>Usti nad Labem</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>66.09999999999999</v>
+        <v>9832</v>
+      </c>
+      <c r="C68" t="n">
+        <v>45</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Liberec</t>
+          <t>Chomutov</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>66.09999999999999</v>
+        <v>9675</v>
+      </c>
+      <c r="C69" t="n">
+        <v>45</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Rychnov nad Kneznou</t>
+          <t>Bruntal</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>66</v>
+        <v>8110</v>
+      </c>
+      <c r="C70" t="n">
+        <v>45</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Pisek</t>
+          <t>Ceske Budejovice</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>65.90000000000001</v>
+        <v>10045</v>
+      </c>
+      <c r="C71" t="n">
+        <v>45</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Breclav</t>
+          <t>Melnik</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>65.8</v>
+        <v>9920</v>
+      </c>
+      <c r="C72" t="n">
+        <v>45</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Usti nad Labem</t>
+          <t>Znojmo</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>65.59999999999999</v>
+        <v>8403</v>
+      </c>
+      <c r="C73" t="n">
+        <v>44</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Blansko</t>
+          <t>Pribram</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>65.59999999999999</v>
+        <v>8754</v>
+      </c>
+      <c r="C74" t="n">
+        <v>44</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Trebic</t>
+          <t>Jihlava</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>65</v>
+        <v>8757</v>
+      </c>
+      <c r="C75" t="n">
+        <v>44</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Nymburk</t>
+          <t>Karlovy Vary</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>63.8</v>
+        <v>8991</v>
+      </c>
+      <c r="C76" t="n">
+        <v>43</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Benesov</t>
+          <t>Strakonice</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>63.4</v>
+        <v>8547</v>
+      </c>
+      <c r="C77" t="n">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -4387,67 +6189,39 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>transaction_year</t>
+          <t>gender</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>total_transactions</t>
+          <t>total_customers</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>2016</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
       </c>
       <c r="B2" t="n">
-        <v>28205</v>
+        <v>2645</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>2017</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
       </c>
       <c r="B3" t="n">
-        <v>91628</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>2018</v>
-      </c>
-      <c r="B4" t="n">
-        <v>133022</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>2019</v>
-      </c>
-      <c r="B5" t="n">
-        <v>196779</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>2020</v>
-      </c>
-      <c r="B6" t="n">
-        <v>284409</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>2021</v>
-      </c>
-      <c r="B7" t="n">
-        <v>314532</v>
+        <v>2724</v>
       </c>
     </row>
   </sheetData>
@@ -4461,61 +6235,931 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:B77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>transaction_type</t>
+          <t>district_name</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>transaction_count</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>total_amount</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>average_amount</t>
+          <t>average_age</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Withdrawal</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>648366</v>
-      </c>
-      <c r="C2" t="n">
-        <v>3014457408</v>
-      </c>
-      <c r="D2" t="n">
-        <v>4649.31</v>
+          <t>Chomutov</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>76.6667</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Credit</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>400209</v>
-      </c>
-      <c r="C3" t="n">
-        <v>3216335973</v>
-      </c>
-      <c r="D3" t="n">
-        <v>8036.64</v>
+          <t>Brno - venkov</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>75.0635</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Bruntal</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>73.6222</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Olomouc</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>72.9231</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Praha - vychod</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>72.8889</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Prerov</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>72.0714</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Rakovnik</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>71.9623</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Klatovy</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>71.8542</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Decin</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>71.7971</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Sumperk</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>71.7869</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Teplice</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>71.5424</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Karlovy Vary</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>71.0698</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Hodonin</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>70.6471</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Trutnov</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>70.6393</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Tabor</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>70.4737</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Praha - zapad</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>70.4464</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Frydek - Mistek</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>70.3488</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Prachatice</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>70.2576</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Semily</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>70.1957</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Sokolov</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>70.1875</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Kutna Hora</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>70.1321</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Pribram</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>70.1136</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Vyskov</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>69.9464</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Znojmo</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>69.9318</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Jihlava</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>69.7500</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Beroun</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>69.7460</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Ceska Lipa</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>69.6545</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Zlin</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>69.5963</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Novy Jicin</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>69.5625</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Jindrichuv Hradec</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>69.4590</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Pelhrimov</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>69.2778</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Tachov</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>69.2712</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Svitavy</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>69.0656</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Domazlice</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>69.0000</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Karvina</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>68.9467</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Nachod</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>68.9211</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Hl.m. Praha</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>68.8552</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Pardubice</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>68.8254</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Kladno</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>68.7800</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Zdar nad Sazavou</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>68.6667</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Strakonice</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>68.5814</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Plzen - mesto</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>68.5600</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Jicin</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>68.5577</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Hradec Kralove</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>68.4727</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Louny</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>68.3846</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Vsetin</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>68.2800</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Cheb</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>68.2642</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Ceske Budejovice</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>68.1333</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Opava</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>68.1000</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Ostrava - mesto</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>68.0056</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Chrudim</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>67.9630</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Havlickuv Brod</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>67.9322</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Melnik</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>67.8222</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Kromeriz</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>67.6094</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Brno - mesto</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>67.4968</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Kolin</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>67.3662</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Uherske Hradiste</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>67.3559</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Cesky Krumlov</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>67.3333</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Jablonec n. Nisou</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>67.2500</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Rokycany</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>66.7963</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Prostejov</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>66.6721</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Plzen - jih</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>66.6182</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Most</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>66.6154</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Usti nad Orlici</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>66.3425</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Plzen - sever</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>66.3333</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Mlada Boleslav</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>66.2754</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Liberec</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>66.1343</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Litomerice</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>66.1250</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Rychnov nad Kneznou</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>66.0000</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Pisek</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>65.8833</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Breclav</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>65.7593</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Usti nad Labem</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>65.6444</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>65.6140</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Trebic</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>65.0370</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Nymburk</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>63.7500</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Benesov</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>63.3696</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -4529,115 +7173,67 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>transaction_month</t>
+          <t>transaction_year</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>transaction_count</t>
+          <t>total_transactions</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>2016</v>
       </c>
       <c r="B2" t="n">
-        <v>122214</v>
+        <v>28205</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>12</v>
+        <v>2017</v>
       </c>
       <c r="B3" t="n">
-        <v>94775</v>
+        <v>91628</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>11</v>
+        <v>2018</v>
       </c>
       <c r="B4" t="n">
-        <v>91890</v>
+        <v>133022</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>10</v>
+        <v>2019</v>
       </c>
       <c r="B5" t="n">
-        <v>90839</v>
+        <v>196779</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>6</v>
+        <v>2020</v>
       </c>
       <c r="B6" t="n">
-        <v>88276</v>
+        <v>284409</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>9</v>
+        <v>2021</v>
       </c>
       <c r="B7" t="n">
-        <v>87955</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>8</v>
-      </c>
-      <c r="B8" t="n">
-        <v>86204</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>7</v>
-      </c>
-      <c r="B9" t="n">
-        <v>83791</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>5</v>
-      </c>
-      <c r="B10" t="n">
-        <v>79931</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>3</v>
-      </c>
-      <c r="B11" t="n">
-        <v>79922</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>4</v>
-      </c>
-      <c r="B12" t="n">
-        <v>76954</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>2</v>
-      </c>
-      <c r="B13" t="n">
-        <v>65824</v>
+        <v>314532</v>
       </c>
     </row>
   </sheetData>
@@ -4667,7 +7263,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>transaction_count</t>
+          <t>total_transactions</t>
         </is>
       </c>
     </row>
@@ -5474,159 +8070,84 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>account_type</t>
+          <t>transaction_type</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>frequency</t>
+          <t>transaction_count</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>total_accounts</t>
+          <t>total_amount</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>average_amount</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>transaction_percentage</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Savings account</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>POPLATEK MESICNE</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>1437</v>
+          <t>Withdrawal</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>648366</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>3014457408.00</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>4649.314443</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>61.83</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>NRI account</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>POPLATEK MESICNE</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>1398</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Salary account</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>POPLATEK MESICNE</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>1332</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>NRI account</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>POPLATEK TYDNE</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Salary account</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>POPLATEK TYDNE</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Savings account</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>POPLATEK TYDNE</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>NRI account</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>POPLATEK PO OBRATU</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Salary account</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>POPLATEK PO OBRATU</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Savings account</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>POPLATEK PO OBRATU</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>26</v>
+          <t>Credit</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>400209</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>3216335973.00</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>8036.640788</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>38.17</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -5640,244 +8161,149 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>account_id</t>
+          <t>operation</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>total_transactions</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>balance</t>
+          <t>average_amount</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>total_amount</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>5891</v>
-      </c>
-      <c r="B2" s="2" t="n">
-        <v>44549</v>
-      </c>
-      <c r="C2" t="n">
-        <v>114092</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Credit in cash </t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>156320</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>15405.45</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2408179630.00</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>96</v>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>44549</v>
-      </c>
-      <c r="C3" t="n">
-        <v>91988.3</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Withdrawal in cash</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>432377</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>5375.85</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2324392424.00</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>3787</v>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>44549</v>
-      </c>
-      <c r="C4" t="n">
-        <v>81497.39999999999</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Electronic funds transfer</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>65226</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>11981.11</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>781479953.00</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>7614</v>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>44549</v>
-      </c>
-      <c r="C5" t="n">
-        <v>62788.6</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Remittance to Another Bank</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>208283</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>3229.44</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>672638484.00</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>108</v>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>44549</v>
-      </c>
-      <c r="C6" t="n">
-        <v>60420.2</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Interest Credit</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>178663</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>149.31</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>26676390.00</t>
+        </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
-        <v>3791</v>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>44549</v>
-      </c>
-      <c r="C7" t="n">
-        <v>60146.1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>3779</v>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>44549</v>
-      </c>
-      <c r="C8" t="n">
-        <v>59783.7</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>122</v>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>44549</v>
-      </c>
-      <c r="C9" t="n">
-        <v>57562.2</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>2367</v>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>44549</v>
-      </c>
-      <c r="C10" t="n">
-        <v>57462.3</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>170</v>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>44549</v>
-      </c>
-      <c r="C11" t="n">
-        <v>57083.4</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>3064</v>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>44549</v>
-      </c>
-      <c r="C12" t="n">
-        <v>55907.4</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>3048</v>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>44549</v>
-      </c>
-      <c r="C13" t="n">
-        <v>49768.1</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>1886</v>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>44549</v>
-      </c>
-      <c r="C14" t="n">
-        <v>49077.9</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>160</v>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>44549</v>
-      </c>
-      <c r="C15" t="n">
-        <v>48645.1</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>3789</v>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>44549</v>
-      </c>
-      <c r="C16" t="n">
-        <v>44784</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>1889</v>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>44549</v>
-      </c>
-      <c r="C17" t="n">
-        <v>41407</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>11362</v>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>44549</v>
-      </c>
-      <c r="C18" t="n">
-        <v>38367.8</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>7753</v>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>44549</v>
-      </c>
-      <c r="C19" t="n">
-        <v>34252</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>3789</v>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>44549</v>
-      </c>
-      <c r="C20" t="n">
-        <v>33684</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>3056</v>
-      </c>
-      <c r="B21" s="2" t="n">
-        <v>44549</v>
-      </c>
-      <c r="C21" t="n">
-        <v>32856.3</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Credit card withdrawal</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>7706</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2261.42</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>17426500.00</t>
+        </is>
       </c>
     </row>
   </sheetData>
